--- a/ETF/Positions2.xlsx
+++ b/ETF/Positions2.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1001"/>
+  <dimension ref="A1:D1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14456,6 +14456,34 @@
         <v>161883.6181671875</v>
       </c>
     </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1002" t="n">
+        <v>157912.1221998047</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>160656.2721998047</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1003" t="n">
+        <v>157912.1221998047</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>160656.2721998047</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETF/Positions2.xlsx
+++ b/ETF/Positions2.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1003"/>
+  <dimension ref="A1:D1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14484,6 +14484,146 @@
         <v>160656.2721998047</v>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1004" t="n">
+        <v>157251.3902667969</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>159995.5402667969</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1005" t="n">
+        <v>157557.8178339844</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>160301.9678339844</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1006" t="n">
+        <v>158714.2567673828</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>161458.4067673828</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1007" t="n">
+        <v>158714.2567673828</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>161458.4067673828</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1008" t="n">
+        <v>158714.2567673828</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>161458.4067673828</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1009" t="n">
+        <v>159767.1148339844</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>162511.2648339844</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1010" t="n">
+        <v>160691.5254005859</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>163435.6754005859</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1011" t="n">
+        <v>160338.8567333985</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>163083.0067333984</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1012" t="n">
+        <v>159590.5697662109</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>162334.7197662109</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1013" t="n">
+        <v>160539.6462667969</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>163283.7962667969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETF/Positions2.xlsx
+++ b/ETF/Positions2.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1013"/>
+  <dimension ref="A1:D1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14624,6 +14624,118 @@
         <v>163283.7962667969</v>
       </c>
     </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1014" t="n">
+        <v>160539.6462667969</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>163283.7962667969</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1015" t="n">
+        <v>160539.6462667969</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>163283.7962667969</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1016" t="n">
+        <v>160451.2784007812</v>
+      </c>
+      <c r="C1016" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>163195.4284007812</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1017" t="n">
+        <v>160414.4902339844</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>163158.6402339844</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1018" t="n">
+        <v>158636.5660998047</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>161380.7160998047</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1019" t="n">
+        <v>159152.8247001953</v>
+      </c>
+      <c r="C1019" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>161896.9747001953</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1020" t="n">
+        <v>157413.7458998047</v>
+      </c>
+      <c r="C1020" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>160157.8958998047</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1021" t="n">
+        <v>157413.7458998047</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>160157.8958998047</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETF/Positions2.xlsx
+++ b/ETF/Positions2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1021"/>
+  <dimension ref="A1:D1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
         <v>1902.18</v>
       </c>
       <c r="D3" t="n">
-        <v>99757.58</v>
+        <v>99757.57999999999</v>
       </c>
     </row>
     <row r="4">
@@ -649,7 +649,7 @@
         <v>1902.18</v>
       </c>
       <c r="D15" t="n">
-        <v>98868.71000000001</v>
+        <v>98868.70999999999</v>
       </c>
     </row>
     <row r="16">
@@ -873,7 +873,7 @@
         <v>1902.18</v>
       </c>
       <c r="D31" t="n">
-        <v>99404.41</v>
+        <v>99404.40999999999</v>
       </c>
     </row>
     <row r="32">
@@ -887,7 +887,7 @@
         <v>1902.18</v>
       </c>
       <c r="D32" t="n">
-        <v>99843.21000000001</v>
+        <v>99843.20999999999</v>
       </c>
     </row>
     <row r="33">
@@ -901,7 +901,7 @@
         <v>1902.18</v>
       </c>
       <c r="D33" t="n">
-        <v>99768.82000000001</v>
+        <v>99768.81999999999</v>
       </c>
     </row>
     <row r="34">
@@ -915,7 +915,7 @@
         <v>1902.18</v>
       </c>
       <c r="D34" t="n">
-        <v>99768.82000000001</v>
+        <v>99768.81999999999</v>
       </c>
     </row>
     <row r="35">
@@ -929,7 +929,7 @@
         <v>1902.18</v>
       </c>
       <c r="D35" t="n">
-        <v>99768.82000000001</v>
+        <v>99768.81999999999</v>
       </c>
     </row>
     <row r="36">
@@ -971,7 +971,7 @@
         <v>1902.18</v>
       </c>
       <c r="D38" t="n">
-        <v>99525.16</v>
+        <v>99525.15999999999</v>
       </c>
     </row>
     <row r="39">
@@ -985,7 +985,7 @@
         <v>1902.18</v>
       </c>
       <c r="D39" t="n">
-        <v>98637.52</v>
+        <v>98637.51999999999</v>
       </c>
     </row>
     <row r="40">
@@ -999,7 +999,7 @@
         <v>1902.18</v>
       </c>
       <c r="D40" t="n">
-        <v>99485.49000000001</v>
+        <v>99485.48999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1013,7 +1013,7 @@
         <v>1902.18</v>
       </c>
       <c r="D41" t="n">
-        <v>99485.49000000001</v>
+        <v>99485.48999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1027,7 +1027,7 @@
         <v>1902.18</v>
       </c>
       <c r="D42" t="n">
-        <v>99485.49000000001</v>
+        <v>99485.48999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1097,7 +1097,7 @@
         <v>1902.18</v>
       </c>
       <c r="D47" t="n">
-        <v>96851.58</v>
+        <v>96851.57999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1111,7 +1111,7 @@
         <v>1902.18</v>
       </c>
       <c r="D48" t="n">
-        <v>96851.58</v>
+        <v>96851.57999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1125,7 +1125,7 @@
         <v>1902.18</v>
       </c>
       <c r="D49" t="n">
-        <v>96851.58</v>
+        <v>96851.57999999999</v>
       </c>
     </row>
     <row r="50">
@@ -1139,7 +1139,7 @@
         <v>1902.18</v>
       </c>
       <c r="D50" t="n">
-        <v>97073.33</v>
+        <v>97073.32999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1153,7 +1153,7 @@
         <v>1902.18</v>
       </c>
       <c r="D51" t="n">
-        <v>98145.36</v>
+        <v>98145.35999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1195,7 +1195,7 @@
         <v>1902.18</v>
       </c>
       <c r="D54" t="n">
-        <v>97425.44</v>
+        <v>97425.43999999999</v>
       </c>
     </row>
     <row r="55">
@@ -1209,7 +1209,7 @@
         <v>1902.18</v>
       </c>
       <c r="D55" t="n">
-        <v>97425.44</v>
+        <v>97425.43999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1223,7 +1223,7 @@
         <v>1902.18</v>
       </c>
       <c r="D56" t="n">
-        <v>97425.44</v>
+        <v>97425.43999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1251,7 +1251,7 @@
         <v>1902.18</v>
       </c>
       <c r="D58" t="n">
-        <v>98064.71000000001</v>
+        <v>98064.70999999999</v>
       </c>
     </row>
     <row r="59">
@@ -1335,7 +1335,7 @@
         <v>1902.18</v>
       </c>
       <c r="D64" t="n">
-        <v>96931.16</v>
+        <v>96931.15999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1349,7 +1349,7 @@
         <v>1902.18</v>
       </c>
       <c r="D65" t="n">
-        <v>96378.02</v>
+        <v>96378.01999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1391,7 +1391,7 @@
         <v>1902.18</v>
       </c>
       <c r="D68" t="n">
-        <v>98222.71000000001</v>
+        <v>98222.70999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1405,7 +1405,7 @@
         <v>1902.18</v>
       </c>
       <c r="D69" t="n">
-        <v>98222.71000000001</v>
+        <v>98222.70999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1419,7 +1419,7 @@
         <v>1902.18</v>
       </c>
       <c r="D70" t="n">
-        <v>98222.71000000001</v>
+        <v>98222.70999999999</v>
       </c>
     </row>
     <row r="71">
@@ -1461,7 +1461,7 @@
         <v>1902.18</v>
       </c>
       <c r="D73" t="n">
-        <v>97996.85000000001</v>
+        <v>97996.84999999999</v>
       </c>
     </row>
     <row r="74">
@@ -1475,7 +1475,7 @@
         <v>1902.18</v>
       </c>
       <c r="D74" t="n">
-        <v>97060.91</v>
+        <v>97060.90999999999</v>
       </c>
     </row>
     <row r="75">
@@ -1531,7 +1531,7 @@
         <v>1902.18</v>
       </c>
       <c r="D78" t="n">
-        <v>96778.96000000001</v>
+        <v>96778.95999999999</v>
       </c>
     </row>
     <row r="79">
@@ -1559,7 +1559,7 @@
         <v>1902.18</v>
       </c>
       <c r="D80" t="n">
-        <v>96309.05</v>
+        <v>96309.04999999999</v>
       </c>
     </row>
     <row r="81">
@@ -1573,7 +1573,7 @@
         <v>1902.18</v>
       </c>
       <c r="D81" t="n">
-        <v>97745.97</v>
+        <v>97745.96999999999</v>
       </c>
     </row>
     <row r="82">
@@ -2021,7 +2021,7 @@
         <v>1902.18</v>
       </c>
       <c r="D113" t="n">
-        <v>98309.24000000001</v>
+        <v>98309.23999999999</v>
       </c>
     </row>
     <row r="114">
@@ -2035,7 +2035,7 @@
         <v>1902.18</v>
       </c>
       <c r="D114" t="n">
-        <v>97346.36</v>
+        <v>97346.35999999999</v>
       </c>
     </row>
     <row r="115">
@@ -2231,7 +2231,7 @@
         <v>1902.18</v>
       </c>
       <c r="D128" t="n">
-        <v>96348.88</v>
+        <v>96348.87999999999</v>
       </c>
     </row>
     <row r="129">
@@ -2357,7 +2357,7 @@
         <v>1902.18</v>
       </c>
       <c r="D137" t="n">
-        <v>97448.58</v>
+        <v>97448.57999999999</v>
       </c>
     </row>
     <row r="138">
@@ -2371,7 +2371,7 @@
         <v>1902.18</v>
       </c>
       <c r="D138" t="n">
-        <v>98020.44</v>
+        <v>98020.43999999999</v>
       </c>
     </row>
     <row r="139">
@@ -2385,7 +2385,7 @@
         <v>1902.18</v>
       </c>
       <c r="D139" t="n">
-        <v>98020.44</v>
+        <v>98020.43999999999</v>
       </c>
     </row>
     <row r="140">
@@ -2399,7 +2399,7 @@
         <v>1902.18</v>
       </c>
       <c r="D140" t="n">
-        <v>98020.44</v>
+        <v>98020.43999999999</v>
       </c>
     </row>
     <row r="141">
@@ -2413,7 +2413,7 @@
         <v>1902.18</v>
       </c>
       <c r="D141" t="n">
-        <v>98022.27</v>
+        <v>98022.26999999999</v>
       </c>
     </row>
     <row r="142">
@@ -2427,7 +2427,7 @@
         <v>1902.18</v>
       </c>
       <c r="D142" t="n">
-        <v>97969.16</v>
+        <v>97969.15999999999</v>
       </c>
     </row>
     <row r="143">
@@ -2455,7 +2455,7 @@
         <v>1902.18</v>
       </c>
       <c r="D144" t="n">
-        <v>99038.83</v>
+        <v>99038.82999999999</v>
       </c>
     </row>
     <row r="145">
@@ -2469,7 +2469,7 @@
         <v>1902.18</v>
       </c>
       <c r="D145" t="n">
-        <v>99897.88</v>
+        <v>99897.87999999999</v>
       </c>
     </row>
     <row r="146">
@@ -2483,7 +2483,7 @@
         <v>1902.18</v>
       </c>
       <c r="D146" t="n">
-        <v>99897.88</v>
+        <v>99897.87999999999</v>
       </c>
     </row>
     <row r="147">
@@ -2497,7 +2497,7 @@
         <v>1902.18</v>
       </c>
       <c r="D147" t="n">
-        <v>99897.88</v>
+        <v>99897.87999999999</v>
       </c>
     </row>
     <row r="148">
@@ -2567,7 +2567,7 @@
         <v>1902.18</v>
       </c>
       <c r="D152" t="n">
-        <v>99808.16</v>
+        <v>99808.15999999999</v>
       </c>
     </row>
     <row r="153">
@@ -2581,7 +2581,7 @@
         <v>1902.18</v>
       </c>
       <c r="D153" t="n">
-        <v>99808.16</v>
+        <v>99808.15999999999</v>
       </c>
     </row>
     <row r="154">
@@ -2595,7 +2595,7 @@
         <v>1902.18</v>
       </c>
       <c r="D154" t="n">
-        <v>99808.16</v>
+        <v>99808.15999999999</v>
       </c>
     </row>
     <row r="155">
@@ -14593,7 +14593,7 @@
         <v>2744.15</v>
       </c>
       <c r="D1011" t="n">
-        <v>163083.0067333984</v>
+        <v>163083.0067333985</v>
       </c>
     </row>
     <row r="1012">
@@ -14733,6 +14733,20 @@
         <v>2744.15</v>
       </c>
       <c r="D1021" t="n">
+        <v>160157.8958998047</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1022" t="n">
+        <v>157413.7458998047</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1022" t="n">
         <v>160157.8958998047</v>
       </c>
     </row>

--- a/ETF/Positions2.xlsx
+++ b/ETF/Positions2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1022"/>
+  <dimension ref="A1:D1030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14750,6 +14750,118 @@
         <v>160157.8958998047</v>
       </c>
     </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1023" t="n">
+        <v>158056.8062666016</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>160800.9562666016</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1024" t="n">
+        <v>158505.6499994141</v>
+      </c>
+      <c r="C1024" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>161249.7999994141</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1025" t="n">
+        <v>159422.2533664063</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>162166.4033664062</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1026" t="n">
+        <v>157495.7516005859</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>160239.9016005859</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1027" t="n">
+        <v>156678.825500586</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>159422.9755005859</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1028" t="n">
+        <v>156678.825500586</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>159422.9755005859</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1029" t="n">
+        <v>156678.825500586</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>159422.9755005859</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1030" t="n">
+        <v>156678.825500586</v>
+      </c>
+      <c r="C1030" t="n">
+        <v>2744.15</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>159422.9755005859</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
